--- a/extenbooks/S201_extenbook.xlsx
+++ b/extenbooks/S201_extenbook.xlsx
@@ -6933,7 +6933,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -8382,11 +8382,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8409,88 +8409,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>US Industrial Production Index</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S201_research.json", "adequacy_report": "Technical/docs/chapters/CH2_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S201_DPR.md", "epr": "Technical/docs/series/S201_EPR.md", "loader": "Technical/code/L01_loaders/L01_S201_load.py", "processor": "Technical/code/P02_processors/P02_S201_construct.py", "validator": "Technical/code/V03_validators/V03_S201_validate.py", "raw_bea": "Technical/data/raw/S201_BEA_LTEG_A173.parquet", "raw_frb": "Technical/data/raw/S201_FRB_G17_BOOK.parquet", "raw_fred": "Technical/data/raw/S201_FRED_INDPRO.parquet", "processed": "Technical/data/processed/S201.parquet", "chopped_csv": "Technical/chopped/S201.csv", "extenbook_xlsx": "Technical/extenbooks/S201_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>subseries_ids</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>["S201-A", "S201-B", "S201-C"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>subsource_ids</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>["BEA_LTEG_1966", "FRB_G17_INDPRO", "FRED_INDPRO"]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S201_extenbook.xlsx
+++ b/extenbooks/S201_extenbook.xlsx
@@ -3010,7 +3010,7 @@
         <v/>
       </c>
       <c r="D169" t="n">
-        <v>491.3418923868783</v>
+        <v>491.3312140064359</v>
       </c>
     </row>
     <row r="170"/>
@@ -6850,7 +6850,7 @@
         <v>2025</v>
       </c>
       <c r="B340" t="n">
-        <v>491.3418923868783</v>
+        <v>491.3312140064359</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>In Shaikh (2016) the series appears as **Figure 2.1** ("US Industrial Production Index, 1860–2010"), opening Chapter 2 ("The Wealth of Nations: A Long View"). Shaikh uses it as the leading empirical illustration of the "system's apparently inexorable tendency toward growth" (p. 56).</t>
+          <t>In Shaikh (2016) the series appears as **Figure 2.1** ("US Industrial Production Index, 1860–2010"), opening Chapter 2 ("Turbulent Trends and Hidden Structures"). Shaikh uses it as the leading empirical illustration of the "system's apparently inexorable tendency toward growth" (p. 56).</t>
         </is>
       </c>
     </row>
@@ -8367,7 +8367,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-18T23:20:17.439678+00:00</t>
+          <t>2026-07-02T13:18:20.751418+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S201_extenbook.xlsx
+++ b/extenbooks/S201_extenbook.xlsx
@@ -6933,7 +6933,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Status**: validated_book_and_extension</t>
         </is>
       </c>
     </row>
@@ -8367,7 +8367,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-02T13:18:20.751418+00:00</t>
+          <t>2026-07-11T03:44:23.989794+00:00</t>
         </is>
       </c>
     </row>
@@ -8382,11 +8382,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8409,6 +8409,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FRB_G17_INDPRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>validated_book_and_extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>book_verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Reconstructs Shaikh (2016) Ch.2 figure; book_period_validated; real data present in chopped CSV; KB-verified.", "date": "2026-06-10"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S201_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S201_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>VREF 2026-07-02: extension subseries S201-C (FRED INDPRO) refreshed to the LATEST FRED/ALFRED vintage (realtime pin 2026-05-27 -&gt; 2026-07-02) per USER RULING. Book rows (S201-A/B, 1860-2010) byte-identical; only 2025 changed: 491.341892 -&gt; 491.331214 (-0.0107, -0.0022%). V03 PASS. See config/VINTAGE_MANIFEST.json + remediation_campaign/evidence_VREF.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>index_1958=100</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
